--- a/data/Negociado_de_Policia/npprDS_ofensores.xlsx
+++ b/data/Negociado_de_Policia/npprDS_ofensores.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\Negociado_de_Policia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EECE46B-B728-4A32-93A0-9F12FB635B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E56B04B-662E-49CC-A45F-FB7A7A961E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6960" yWindow="1404" windowWidth="17280" windowHeight="9420" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13056" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2019" sheetId="15" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="2023" sheetId="12" r:id="rId5"/>
     <sheet name="2024" sheetId="10" r:id="rId6"/>
     <sheet name="2025" sheetId="14" r:id="rId7"/>
+    <sheet name="2026" sheetId="16" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="18">
   <si>
     <t>Mujeres</t>
   </si>
@@ -1733,4 +1734,193 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31BC1AE1-F278-4BE4-9B5A-B417B2BBCD4F}">
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <v>19</v>
+      </c>
+      <c r="C7">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>24</v>
+      </c>
+      <c r="C8">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9">
+        <v>18</v>
+      </c>
+      <c r="C9">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10">
+        <v>15</v>
+      </c>
+      <c r="C10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11">
+        <v>7</v>
+      </c>
+      <c r="C11">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12">
+        <v>6</v>
+      </c>
+      <c r="C12">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16">
+        <v>49</v>
+      </c>
+      <c r="C16">
+        <v>203</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>